--- a/forms/trg/Formulir_TRG_medi-edu.xlsx
+++ b/forms/trg/Formulir_TRG_medi-edu.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B27)</f>
+        <f>COUNTA(Anggota!B5:B28)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F27)</f>
+        <f>COUNTA(Anggota!F5:F28)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,24 +913,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Irwin Aras</t>
+          <t>Prof. dr. Budu, Ph.D.,Sp.M., MMedEd</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -950,12 +946,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Sri Asriyani</t>
+          <t>Irwin Aras</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -987,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Bau Dilam Ardyansyah</t>
+          <t>Sri Asriyani</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1024,12 +1020,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Asty Amalia Nurhadi</t>
+          <t>Bau Dilam Ardyansyah</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1061,12 +1057,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Andi Ratih Radiah Iskandar</t>
+          <t>Asty Amalia Nurhadi</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1098,12 +1094,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Rezky Fajrianti Umar</t>
+          <t>Andi Ratih Radiah Iskandar</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1135,18 +1131,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dhiyaul Athifah M. Jasri</t>
+          <t>Rezky Fajrianti Umar</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1168,18 +1168,18 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Margo Brewer</t>
+          <t>Dhiyaul Athifah M. Jasri</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1201,22 +1201,18 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dwi Sartika</t>
+          <t>Margo Brewer</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Researchers</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>External Collaborator</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1238,17 +1234,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Amila Saliha Mustarin</t>
+          <t>Dwi Sartika</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Graduate Student</t>
+          <t>Researchers</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Indah Nurul Khairunnisa</t>
+          <t>Amila Saliha Mustarin</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1310,10 +1306,26 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Indah Nurul Khairunnisa</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Medical Education Research Group advances innovation in health professions education through collaborative, evidence-based, and technology-enhanced approaches. We strengthen teaching, assessment, curriculum, leadership, and professionalism while developing impactful interprofessional education models. Our mission is to produce high-quality research, foster partnerships, and prepare ethical, practice-ready healthcare professionals worldwide across diverse global settings.</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1321,7 +1333,11 @@
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1510,15 +1526,32 @@
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="12" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
